--- a/Catálogo Completo de Items.xlsx
+++ b/Catálogo Completo de Items.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\arkanor-assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B832D3-9D88-47BA-A902-C74E0563949C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6BD850-6EAF-472A-83C1-D841F555F0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Artefactos" sheetId="3" r:id="rId1"/>
+    <sheet name="Ropas" sheetId="8" r:id="rId1"/>
     <sheet name="Varios" sheetId="7" r:id="rId2"/>
+    <sheet name="Para Copiar" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,61 +32,800 @@
     <author>Lenovo</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{AA1B420F-3750-41C2-BE6E-CECB80DB7573}">
-      <text/>
-    </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{F8657CE4-A87E-4934-800B-35488E7158F4}">
-      <text/>
-    </comment>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{08B58F5C-D9E0-4714-81E7-A8A1E1881E3C}">
-      <text/>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{75089233-5BF2-473B-AAE1-EFDD864CE650}">
-      <text/>
-    </comment>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{ACDBB28C-6F68-4F50-B0CB-B2A15092307A}">
-      <text/>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{0FC9644E-DDF4-413B-B6A4-58A18C194E45}">
-      <text/>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{619BA490-BE1A-4D66-B481-0782012C71D0}">
-      <text/>
-    </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{971C0B81-2375-4E26-97F0-B59556AC305A}">
-      <text/>
-    </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{5D02EBB7-B13B-41CE-9DD3-B5EEE1928B48}">
-      <text/>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{80A0ECC5-9181-44E5-B7BD-955A8D600348}">
-      <text/>
-    </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{200CFB82-2E0D-4A0A-996A-92EF1C218BBF}">
-      <text/>
-    </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{A91C6D69-2C99-461B-817D-060D05062323}">
-      <text/>
-    </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{020A7563-7113-4D73-B99F-6DD6F8AB28F3}">
-      <text/>
-    </comment>
-    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{26406FEC-C2DF-42E7-8406-7AAF449FAE21}">
-      <text/>
-    </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{DEBDF6D2-43F9-435C-8FC3-31B129D702D5}">
-      <text/>
-    </comment>
-    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{D187756C-F5FF-4E82-9480-FFEA91F1642D}">
-      <text/>
-    </comment>
-    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{2F98F822-6A36-4A21-88B3-D7C665213E04}">
-      <text/>
-    </comment>
-    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{E806EB14-DA63-41FD-9A53-DC874FA79870}">
-      <text/>
-    </comment>
-    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{56D8B43E-DC9A-4BB0-88D6-20366B0DB46E}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{9C2D096F-0EF3-4F23-8F76-CC7B6C0C0522}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y broche color blanco: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Cobertura común en la moda casual alfarhim con una capucha añadida.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{426D5D96-D4CE-4AD7-B26A-0DF47CACE516}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Pantalon abombado con botones negro: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Vestimenta suelta y cómoda de usos variados  usada principalmente por los duergar de Morgrim.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AP3" authorId="0" shapeId="0" xr:uid="{ECBD33E4-C4E5-4FCA-A215-DE1C6E8DE74D}">
+      <text/>
+    </comment>
+    <comment ref="BJ3" authorId="0" shapeId="0" xr:uid="{1560673B-D399-410C-88D3-8A87D320FE5B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Vestido cenido de aldeana marrón: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ropa generalmente utilizada por mujeres plebeyas en los reinos de Costa Dorada y Lunevale.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="CD3" authorId="0" shapeId="0" xr:uid="{FDC86D7B-9775-4487-9A83-9593125841F3}">
+      <text/>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{31B00BFA-1BC8-4F73-9F9F-77E0383E3AA4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y broche color celeste: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Cobertura común en la moda casual alfarhim con una capucha añadida.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V4" authorId="0" shapeId="0" xr:uid="{0A99EBA1-4DF6-47C4-AC05-6837BF7E3222}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Pantalon abombado con botones negro: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Vestimenta suelta y cómoda de usos variados  usada principalmente por los duergar de Morgrim.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AP4" authorId="0" shapeId="0" xr:uid="{D954E5DF-D9B0-41A9-84FC-7F779FFE4D0D}">
+      <text/>
+    </comment>
+    <comment ref="BJ4" authorId="0" shapeId="0" xr:uid="{51667FAC-BFED-4C5D-A431-5AD38BAC49D0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Vestido cenido de aldeana rojizo: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ropa generalmente utilizada por mujeres plebeyas en los reinos de Costa Dorada y Lunevale.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="CD4" authorId="0" shapeId="0" xr:uid="{2FAB92D9-77F9-46C3-8875-5E9D2CDE0F33}">
+      <text/>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{13016D9F-5D4C-4083-9D27-BF8A81189F80}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y broche color negro: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Cobertura común en la moda casual alfarhim con una capucha añadida.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{ABD76593-4B68-428F-AAE6-74D943859A0C}">
+      <text/>
+    </comment>
+    <comment ref="AP5" authorId="0" shapeId="0" xr:uid="{119CA647-A464-4FD3-BB24-8EBFC918C756}">
+      <text/>
+    </comment>
+    <comment ref="BJ5" authorId="0" shapeId="0" xr:uid="{58E44CCD-E8D5-4C40-91A0-000D45C42154}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Vestido cenido de aldeana amarillento: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ropa generalmente utilizada por mujeres plebeyas en los reinos de Costa Dorada y Lunevale.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="CD5" authorId="0" shapeId="0" xr:uid="{48FA0EE9-4056-4726-B71B-C846F2F38182}">
+      <text/>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{653975FF-8E83-4836-9AC4-373F1AF43564}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y broche color rojo: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Cobertura común en la moda casual alfarhim con una capucha añadida.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V6" authorId="0" shapeId="0" xr:uid="{28471288-6797-4447-BEBA-D2E60AED9891}">
+      <text/>
+    </comment>
+    <comment ref="AP6" authorId="0" shapeId="0" xr:uid="{2A7671A4-48BF-4BF6-B5D0-E52572574B65}">
+      <text/>
+    </comment>
+    <comment ref="BJ6" authorId="0" shapeId="0" xr:uid="{EE398084-3AE0-40C2-9714-ABB6F36AFD75}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Vestido cenido de aldeana: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ropa generalmente utilizada por mujeres plebeyas en los reinos de Costa Dorada y Lunevale.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="CD6" authorId="0" shapeId="0" xr:uid="{972E68B3-C173-4C22-96E9-B9F861D02B3E}">
+      <text/>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{95AE113F-9888-439C-8528-AF5E8A5FED5E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y broche color verde: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Cobertura común en la moda casual alfarhim con una capucha añadida.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V7" authorId="0" shapeId="0" xr:uid="{A6EE5A4F-D331-49A3-9D45-BD0D37F5640E}">
+      <text/>
+    </comment>
+    <comment ref="AP7" authorId="0" shapeId="0" xr:uid="{8292D841-FF05-428D-9AEE-D3186FE5D8C2}">
+      <text/>
+    </comment>
+    <comment ref="BJ7" authorId="0" shapeId="0" xr:uid="{D8D27CD4-940B-4ECE-B9C3-407CFB31B566}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Vestido Ceñido de Viaje con Capucha: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Práctica ropa de viajero con una capucha para abrigar la cabeza y, a la vez, dar un sutil aire de misterio.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="CD7" authorId="0" shapeId="0" xr:uid="{C981A99C-4539-4022-958B-7D5E12713A48}">
+      <text/>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{685D1456-52EB-4D52-9E33-1026B09E2154}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y prendedor blanca: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Capa con capucha común y corriente, puede conseguirse en cualquier parte del continente con pocas variantes diferenciales.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V8" authorId="0" shapeId="0" xr:uid="{6556DD94-AAF4-45C9-9A9A-C10B1E4E10A3}">
+      <text/>
+    </comment>
+    <comment ref="AP8" authorId="0" shapeId="0" xr:uid="{00F6C49A-E559-406D-8FCE-DD32ECFC47E5}">
+      <text/>
+    </comment>
+    <comment ref="BJ8" authorId="0" shapeId="0" xr:uid="{D53B376A-1F17-46C7-B39D-C1F889CCC641}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Camisa acordonada con volados: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Ropaje simple, de clases medias, utilizado en los reinos de Costa Dorada y Lunevale generalmente.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="CD8" authorId="0" shapeId="0" xr:uid="{62D68395-3B4C-4DA2-9D25-803E9B0144E5}">
+      <text/>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{AF4496CA-E727-4EAB-A766-E112A0460CA8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y prendedor celeste: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Capa con capucha común y corriente, puede conseguirse en cualquier parte del continente con pocas variantes diferenciales.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V9" authorId="0" shapeId="0" xr:uid="{F5469315-FC89-4E6E-AFB4-43F3437E266C}">
+      <text/>
+    </comment>
+    <comment ref="AP9" authorId="0" shapeId="0" xr:uid="{8B2A405A-1156-4476-82D9-579AE03FA7B9}">
+      <text/>
+    </comment>
+    <comment ref="BJ9" authorId="0" shapeId="0" xr:uid="{F7D106BF-9C4B-4101-B490-AC80ADCF86B1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Túnica de Monje de la Luz: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Atuendo oficial de los miembros iniciados en la religión de la luz.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="CD9" authorId="0" shapeId="0" xr:uid="{D957E974-6E56-482E-85E4-398EFB7B3499}">
+      <text/>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{59BBB06C-71E4-4FB0-A26E-54FD6214DB9D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y prendedor marrón: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Capa con capucha común y corriente, puede conseguirse en cualquier parte del continente con pocas variantes diferenciales.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V10" authorId="0" shapeId="0" xr:uid="{80DF7EC1-5EEE-4072-B80A-8B3039F6E16E}">
+      <text/>
+    </comment>
+    <comment ref="AP10" authorId="0" shapeId="0" xr:uid="{2EC6D559-1B66-4F37-BFAC-712070D4E9AA}">
+      <text/>
+    </comment>
+    <comment ref="BJ10" authorId="0" shapeId="0" xr:uid="{95FF5645-4C03-4794-84C9-8CF0FA09BAE8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Camisa duergar norteña: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Atuendo común muy usado por los ciudadanos masculinos de los reinos duergar en el norte de las montañas de Kharund.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="CD10" authorId="0" shapeId="0" xr:uid="{3F7FC67E-F419-45B4-B40A-53EB50B70E33}">
+      <text/>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{9957C782-789E-47BB-B0B2-F6CC539BF703}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y prendedor roja: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Capa con capucha común y corriente, puede conseguirse en cualquier parte del continente con pocas variantes diferenciales.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V11" authorId="0" shapeId="0" xr:uid="{CEB6C9F8-C179-4202-9389-CD2E0E6547BE}">
+      <text/>
+    </comment>
+    <comment ref="AP11" authorId="0" shapeId="0" xr:uid="{5D9CA83F-2D91-4038-A5CE-7A4AA23143B1}">
+      <text/>
+    </comment>
+    <comment ref="BJ11" authorId="0" shapeId="0" xr:uid="{FBC9BC16-8CE6-4B86-88B3-3310F4493602}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Vestido ceñido de plebeya marrón con delantal: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Ropa común, generalmente femeninta, utilizado mayormente entre los reinos que componen Valtherra.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="CD11" authorId="0" shapeId="0" xr:uid="{0BF453F4-BDFF-4508-88DD-21E981BDCB6B}">
+      <text/>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{9F9A0879-EFE6-45CD-B6E1-E9F3601FC4F3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa con capucha y prendedor verte: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Capa con capucha común y corriente, puede conseguirse en cualquier parte del continente con pocas variantes diferenciales.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V12" authorId="0" shapeId="0" xr:uid="{AA9BEFD1-D1D8-40F7-BAC6-B404DEA84938}">
+      <text/>
+    </comment>
+    <comment ref="AP12" authorId="0" shapeId="0" xr:uid="{5DCB7287-31A7-4566-8309-37261766C50A}">
+      <text/>
+    </comment>
+    <comment ref="BJ12" authorId="0" shapeId="0" xr:uid="{9A19EA7E-7C4B-4AF3-A70A-8C54AB19543B}">
+      <text/>
+    </comment>
+    <comment ref="CD12" authorId="0" shapeId="0" xr:uid="{A562E15B-01F0-4F34-81C2-13B9DC233106}">
+      <text/>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{C89CF29F-401E-428F-8F07-DD36AEEA48E6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa de Hombros: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Vestimenta que cubre hombros y cuello, utilizado por campesinos con variaciones simples pero también por miembros del clero de la religión de la luz, como símbolo de entrega y dedicación al culto.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V13" authorId="0" shapeId="0" xr:uid="{5046E79F-AD89-4674-872D-8CFA3E5646ED}">
+      <text/>
+    </comment>
+    <comment ref="AP13" authorId="0" shapeId="0" xr:uid="{38CC9220-6C8E-4FDB-B93E-8AE608521845}">
+      <text/>
+    </comment>
+    <comment ref="BJ13" authorId="0" shapeId="0" xr:uid="{DBFE5DA4-9965-469C-8A40-A9B53D35F5A1}">
+      <text/>
+    </comment>
+    <comment ref="CD13" authorId="0" shapeId="0" xr:uid="{828DE3F6-1A21-4458-BCBA-8CBB6D3A45C0}">
+      <text/>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{FF123582-0224-4FBB-BCCA-6732D00828AE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Capa elegante morgrimesa: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Sofisticado tapado usado por las clases más poderosas y  familias de jefes laboratores de Morgrim.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V14" authorId="0" shapeId="0" xr:uid="{535AB6A6-69CA-41F6-93FB-DBD513B857EC}">
+      <text/>
+    </comment>
+    <comment ref="AP14" authorId="0" shapeId="0" xr:uid="{6CA5FAF4-D99A-4E64-8DB4-171B07B6E54C}">
+      <text/>
+    </comment>
+    <comment ref="BJ14" authorId="0" shapeId="0" xr:uid="{CECC45B3-79F5-42C5-8BBC-73A06C4DD258}">
+      <text/>
+    </comment>
+    <comment ref="CD14" authorId="0" shapeId="0" xr:uid="{94835ED0-143F-4625-89DF-9CE41A269926}">
+      <text/>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{180A471E-0D29-4551-B5F4-889A50D348F6}">
+      <text/>
+    </comment>
+    <comment ref="V15" authorId="0" shapeId="0" xr:uid="{058A60DF-1CF1-4809-B840-FD0584D1B044}">
+      <text/>
+    </comment>
+    <comment ref="AP15" authorId="0" shapeId="0" xr:uid="{FA53D8B2-C05D-4865-A45A-DA6E0A1209B4}">
+      <text/>
+    </comment>
+    <comment ref="BJ15" authorId="0" shapeId="0" xr:uid="{D3A593FB-A65A-45BC-A6F8-421F4D2E712E}">
+      <text/>
+    </comment>
+    <comment ref="CD15" authorId="0" shapeId="0" xr:uid="{9EE4BEFC-B2CE-4BCB-96FA-D69F61179811}">
+      <text/>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{91765B4B-DACA-4351-BD7D-FB3310B4D8A8}">
+      <text/>
+    </comment>
+    <comment ref="V16" authorId="0" shapeId="0" xr:uid="{4500DBF4-2B94-431D-9776-3033A405FABF}">
+      <text/>
+    </comment>
+    <comment ref="AP16" authorId="0" shapeId="0" xr:uid="{D1DBAB60-528A-4E94-B54D-349AA4128B79}">
+      <text/>
+    </comment>
+    <comment ref="BJ16" authorId="0" shapeId="0" xr:uid="{E3225CE2-28BE-4845-B3B7-1DA7DDD7D520}">
+      <text/>
+    </comment>
+    <comment ref="CD16" authorId="0" shapeId="0" xr:uid="{4AB742A9-DB50-4277-BB7E-96AD50ADBB2A}">
+      <text/>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{5F599675-5503-4314-B92A-80CC793A1BAC}">
+      <text/>
+    </comment>
+    <comment ref="V17" authorId="0" shapeId="0" xr:uid="{F60B3FCD-2064-4541-BB26-28C7D603AB2B}">
+      <text/>
+    </comment>
+    <comment ref="AP17" authorId="0" shapeId="0" xr:uid="{8CAD8288-B86C-4000-97D9-F5768F85159D}">
+      <text/>
+    </comment>
+    <comment ref="BJ17" authorId="0" shapeId="0" xr:uid="{CB191B6F-CE81-42CE-95E1-2750F5469898}">
+      <text/>
+    </comment>
+    <comment ref="CD17" authorId="0" shapeId="0" xr:uid="{5B4A81D7-5A6B-4759-8793-28E5069348A7}">
+      <text/>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{E321CB6A-DF38-4D7B-9E99-9CAE0DF53954}">
+      <text/>
+    </comment>
+    <comment ref="V18" authorId="0" shapeId="0" xr:uid="{C78DC17E-097D-49D9-AA1A-B6E63715773B}">
+      <text/>
+    </comment>
+    <comment ref="AP18" authorId="0" shapeId="0" xr:uid="{A40C2241-1915-4D78-AD14-8EAADD6FF22E}">
+      <text/>
+    </comment>
+    <comment ref="BJ18" authorId="0" shapeId="0" xr:uid="{0A4BF7E6-6253-4353-B8DF-54F33AAC0E72}">
+      <text/>
+    </comment>
+    <comment ref="CD18" authorId="0" shapeId="0" xr:uid="{189FEE4E-FB73-4581-8AEE-43173924143E}">
+      <text/>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{E2B8B357-4166-496E-90F3-4B80491FBC5B}">
+      <text/>
+    </comment>
+    <comment ref="V19" authorId="0" shapeId="0" xr:uid="{E80A515B-D050-4223-ADEB-2469EB4BE540}">
+      <text/>
+    </comment>
+    <comment ref="AP19" authorId="0" shapeId="0" xr:uid="{730D9812-CA50-4972-978A-4858E1B34886}">
+      <text/>
+    </comment>
+    <comment ref="BJ19" authorId="0" shapeId="0" xr:uid="{F53143DE-AE52-4CF4-9215-A0F9261C1295}">
+      <text/>
+    </comment>
+    <comment ref="CD19" authorId="0" shapeId="0" xr:uid="{A4D324F9-5F62-4884-973D-3D4C5C0B591E}">
+      <text/>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{BDB1F8F2-98D6-4142-B344-9362A2404650}">
+      <text/>
+    </comment>
+    <comment ref="V20" authorId="0" shapeId="0" xr:uid="{49E13E63-8870-4F09-8F2C-D441203A862B}">
+      <text/>
+    </comment>
+    <comment ref="AP20" authorId="0" shapeId="0" xr:uid="{3FE6E8A9-CB91-4471-AA94-0B7326DA123C}">
+      <text/>
+    </comment>
+    <comment ref="BJ20" authorId="0" shapeId="0" xr:uid="{9AD0BD75-2107-45E8-AE63-8B4914DAFF4B}">
+      <text/>
+    </comment>
+    <comment ref="CD20" authorId="0" shapeId="0" xr:uid="{7AD76B66-2B7A-467B-83AC-19647091BCB6}">
+      <text/>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0" xr:uid="{A0A26E3E-A23B-4963-B6EE-FD1948046D28}">
+      <text/>
+    </comment>
+    <comment ref="V21" authorId="0" shapeId="0" xr:uid="{043CDC67-BF70-4A3C-979F-054A40588EF6}">
+      <text/>
+    </comment>
+    <comment ref="AP21" authorId="0" shapeId="0" xr:uid="{4C0AD7F2-88A4-4521-9F6F-BE20C08DD15B}">
+      <text/>
+    </comment>
+    <comment ref="BJ21" authorId="0" shapeId="0" xr:uid="{A9CD2663-6B43-4F8E-A453-665A76B17816}">
+      <text/>
+    </comment>
+    <comment ref="CD21" authorId="0" shapeId="0" xr:uid="{35F45147-D6A5-462C-85E4-E62E432470B1}">
       <text/>
     </comment>
   </commentList>
@@ -98,7 +838,161 @@
     <author>Lenovo</author>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{0E58FE0B-ADD7-4150-9618-38ED3D5A048E}">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{B0F520F8-0FBC-4E03-819B-BF78CEE8F5DE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Cadena: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Una pieza de apróximadamente 1 metro de eslabones de metal enlazados.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{CECEAD7D-5474-4AA1-AD6B-8D2C2BFD6E25}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Piedra Grande: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Una piedra lo bastante grande como para aplastarte dolorosamente un dedo pero lo suficientemente portatil como para llevarla en algún espacio relativamente amplio de una mochila.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{2A815C04-2CFF-4148-9E12-1F35837AD67A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Arrojadiza: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">El arma se considera también un arma a distancia y puedes arrojarla aplicando para la acción las tiradas de chance y daño pertinentes a los ataque a distancia.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{25568244-D866-4DB2-A469-633CE9D998FD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Aturdir: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>realiza un ataque que, si es exitoso, produce aturdir en el objetivo, 2 RES.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{0521D605-5805-4ED9-AA36-5A6F133F9C41}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Piedra Mediana: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Una piedra más grande que una piedra pequeña pero más pequeña que una piedra grande, las tribus nómades las suelen llamar piedras bastardas. Posee capacidad de chichonizar un cráneo objetivo un poco mayor que las pequeñas.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{60E90822-2456-4A18-A1CC-0710F00B3FB8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">Arrojadiza: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="20"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">El arma se considera también un arma a distancia y puedes arrojarla aplicando para la acción las tiradas de chance y daño pertinentes a los ataque a distancia.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{0E58FE0B-ADD7-4150-9618-38ED3D5A048E}">
       <text>
         <r>
           <rPr>
@@ -124,7 +1018,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{28D129CA-4F95-4AF5-84E7-B26CC9E3DC93}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{28D129CA-4F95-4AF5-84E7-B26CC9E3DC93}">
       <text>
         <r>
           <rPr>
@@ -150,7 +1044,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{0521D605-5805-4ED9-AA36-5A6F133F9C41}">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{75983040-C783-4A4A-AD87-97D21DE0DFC7}">
       <text>
         <r>
           <rPr>
@@ -161,7 +1055,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">Piedra Mediana: </t>
+          <t xml:space="preserve">Cuaderno Pequeño: </t>
         </r>
         <r>
           <rPr>
@@ -171,120 +1065,10 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">Una piedra más grande que una piedra pequeña pero más pequeña que una piedra grande, las tribus nómades las suelen llamar piedras bastardas. Posee capacidad de chichonizar un cráneo objetivo un poco mayor que las pequeñas.
-</t>
+          <t>Una libreta no muy grande con hojas cocidas y tapas duras simple, está en blanco para que se puedan registrar anotaciones.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{60E90822-2456-4A18-A1CC-0710F00B3FB8}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Arrojadiza: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">El arma se considera también un arma a distancia y puedes arrojarla aplicando para la acción las tiradas de chance y daño pertinentes a los ataque a distancia.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{CECEAD7D-5474-4AA1-AD6B-8D2C2BFD6E25}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Piedra Grande: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Una piedra lo bastante grande como para aplastarte dolorosamente un dedo pero lo suficientemente portatil como para llevarla en algún espacio relativamente amplio de una mochila.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{2A815C04-2CFF-4148-9E12-1F35837AD67A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Arrojadiza: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">El arma se considera también un arma a distancia y puedes arrojarla aplicando para la acción las tiradas de chance y daño pertinentes a los ataque a distancia.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{25568244-D866-4DB2-A469-633CE9D998FD}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t xml:space="preserve">Aturdir: </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="20"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>realiza un ataque que, si es exitoso, produce aturdir en el objetivo, 2 RES.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{B0F520F8-0FBC-4E03-819B-BF78CEE8F5DE}">
-      <text/>
-    </comment>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{75983040-C783-4A4A-AD87-97D21DE0DFC7}">
-      <text/>
-    </comment>
     <comment ref="B7" authorId="0" shapeId="0" xr:uid="{FFB71A49-E410-437D-8867-574E1E9279A0}">
       <text/>
     </comment>
@@ -325,6 +1109,73 @@
       <text/>
     </comment>
     <comment ref="B20" authorId="0" shapeId="0" xr:uid="{875534AD-EE80-4248-B343-A3D1F5BECFF6}">
+      <text/>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Lenovo</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{AA1B420F-3750-41C2-BE6E-CECB80DB7573}">
+      <text/>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{F8657CE4-A87E-4934-800B-35488E7158F4}">
+      <text/>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{08B58F5C-D9E0-4714-81E7-A8A1E1881E3C}">
+      <text/>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{75089233-5BF2-473B-AAE1-EFDD864CE650}">
+      <text/>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{ACDBB28C-6F68-4F50-B0CB-B2A15092307A}">
+      <text/>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{0FC9644E-DDF4-413B-B6A4-58A18C194E45}">
+      <text/>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{619BA490-BE1A-4D66-B481-0782012C71D0}">
+      <text/>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{971C0B81-2375-4E26-97F0-B59556AC305A}">
+      <text/>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{5D02EBB7-B13B-41CE-9DD3-B5EEE1928B48}">
+      <text/>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{80A0ECC5-9181-44E5-B7BD-955A8D600348}">
+      <text/>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{200CFB82-2E0D-4A0A-996A-92EF1C218BBF}">
+      <text/>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{A91C6D69-2C99-461B-817D-060D05062323}">
+      <text/>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{020A7563-7113-4D73-B99F-6DD6F8AB28F3}">
+      <text/>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{26406FEC-C2DF-42E7-8406-7AAF449FAE21}">
+      <text/>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{DEBDF6D2-43F9-435C-8FC3-31B129D702D5}">
+      <text/>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{D187756C-F5FF-4E82-9480-FFEA91F1642D}">
+      <text/>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{2F98F822-6A36-4A21-88B3-D7C665213E04}">
+      <text/>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0" xr:uid="{E806EB14-DA63-41FD-9A53-DC874FA79870}">
+      <text/>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0" xr:uid="{56D8B43E-DC9A-4BB0-88D6-20366B0DB46E}">
       <text/>
     </comment>
   </commentList>
@@ -332,7 +1183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="52">
   <si>
     <t>Nombre</t>
   </si>
@@ -367,9 +1218,6 @@
     <t>Ícono y Descripción</t>
   </si>
   <si>
-    <t>Efectos</t>
-  </si>
-  <si>
     <t>Peso</t>
   </si>
   <si>
@@ -396,12 +1244,108 @@
   <si>
     <t>Ligera</t>
   </si>
+  <si>
+    <t>Efectos u observaciones</t>
+  </si>
+  <si>
+    <t>Efectos u Observaciones</t>
+  </si>
+  <si>
+    <t>Cadena</t>
+  </si>
+  <si>
+    <t>Cuaderno Pequeño</t>
+  </si>
+  <si>
+    <t>Vestido ceñido de aldeana marrón</t>
+  </si>
+  <si>
+    <t>Vestido ceñido de aldeana rojizo</t>
+  </si>
+  <si>
+    <t>Vestido ceñido de aldeana amarillento</t>
+  </si>
+  <si>
+    <t>Vestido ceñido de aldeana</t>
+  </si>
+  <si>
+    <t>Vestido Ceñido de Viaje con Capucha</t>
+  </si>
+  <si>
+    <t>Camisa acordonada con volados</t>
+  </si>
+  <si>
+    <t>Túnica de Monje de la Luz</t>
+  </si>
+  <si>
+    <t>Capa con capucha y broche color verde</t>
+  </si>
+  <si>
+    <t>Capa con capucha y broche color negro</t>
+  </si>
+  <si>
+    <t>Capa con capucha y broche color celeste</t>
+  </si>
+  <si>
+    <t>Capa con capucha y broche color rojo</t>
+  </si>
+  <si>
+    <t>Capa con capucha y broche color blanco</t>
+  </si>
+  <si>
+    <t>Capa con capucha y prendedor blanca</t>
+  </si>
+  <si>
+    <t>Capa con capucha y prendedor verde</t>
+  </si>
+  <si>
+    <t>Capa con capucha y prendedor celeste</t>
+  </si>
+  <si>
+    <t>Capa con capucha y prendedor marrón</t>
+  </si>
+  <si>
+    <t>Capa con capucha y prendedor Roja</t>
+  </si>
+  <si>
+    <t>Hombros</t>
+  </si>
+  <si>
+    <t>Piernas</t>
+  </si>
+  <si>
+    <t>Cabeza</t>
+  </si>
+  <si>
+    <t>Torso</t>
+  </si>
+  <si>
+    <t>Manos y Pies</t>
+  </si>
+  <si>
+    <t>Capa de hombros</t>
+  </si>
+  <si>
+    <t>Camisa duergar norteña</t>
+  </si>
+  <si>
+    <t>Capa elegante morgrimesa</t>
+  </si>
+  <si>
+    <t>Pantalón abombado con botones marrón</t>
+  </si>
+  <si>
+    <t>Pantalón abombado con botones negro</t>
+  </si>
+  <si>
+    <t>Vestido ceñido de plebeya marrón con delantal</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,8 +1409,13 @@
       <color theme="1"/>
       <name val="Dominican"/>
     </font>
+    <font>
+      <sz val="50"/>
+      <color theme="1"/>
+      <name val="Dominican"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,8 +1440,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -645,11 +1600,112 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -702,10 +1758,58 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -730,14 +1834,1484 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>68035</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>752035</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>684000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0601EAD4-EA2B-4597-498B-418D696CA087}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1619249" y="734786"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>54428</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>738428</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>684000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagen 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD3E00B9-2E11-02D9-901D-13743A015EC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1605642" y="1469571"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>738429</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>684000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3C98C98-C55F-EB4C-65DF-5EED4DA0CFBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1605643" y="2190751"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>738428</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>684000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagen 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{654353AE-6E5B-B690-FCB1-158D922C679F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1605642" y="2911928"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>738428</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>684000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C071D7B-3FD6-EDC9-E172-558B2411C946}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1605642" y="3633107"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>738428</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>684000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Imagen 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD03A279-8A64-A817-4CE8-F14CA99CC405}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1605642" y="4354285"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>40821</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>724821</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>684000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Imagen 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B206E7D1-DC26-13AE-2699-669E17F205CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1592035" y="5075464"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>38420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>738428</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>8044</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Imagen 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6AD8A64-940B-A27D-D3F4-3B4E1C6904D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1612046" y="5865479"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740030</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>3243</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Imagen 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98B0A4F5-8069-0AAF-050C-664D02F1FD08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613648" y="6589059"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740030</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>706412</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Imagen 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E082DDF-431E-D319-3EA5-BD0B5F1716B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613648" y="7306236"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>33619</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740030</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>3243</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Imagen 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECB7C904-0346-7686-FF20-D765055B4EFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613648" y="8045825"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740030</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>706412</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Imagen 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3010BA1-FAD7-10ED-9039-5D69D8DA61FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613648" y="8763000"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740030</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>3243</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Imagen 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6ED7CB6-79CB-7D66-AA4D-89FBEA34C6EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613648" y="9502589"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740030</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>706411</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Imagen 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D856BED7-6C63-E894-55E6-9AAD192E82D5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613648" y="10219764"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740030</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3244</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Imagen 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A87059DA-517B-915A-E938-082B37265000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613648" y="10959353"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56029</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>33617</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740029</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>3241</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Imagen 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F730598B-62B0-0D4C-F0B1-FB142F1DD960}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613647" y="11687735"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740030</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3243</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Imagen 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B28FD1D-1A5C-397A-191A-88C3BC4AC543}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613648" y="12416118"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>68035</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>13607</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="684000" cy="684000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Imagen 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6848A516-95F3-4DC8-A004-A1A56AC09C3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1626671" y="1468334"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="684000" cy="684000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Imagen 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85B01568-FA6C-42BA-BA78-77FE51728625}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613064" y="2209305"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="684000" cy="684000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Imagen 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96F953BC-7245-4199-9003-ED3978821BE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613065" y="2936670"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="684000" cy="684000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Imagen 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2922F5FC-E7A5-418D-877F-4C28A140C394}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613064" y="3664032"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="684000" cy="684000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="52" name="Imagen 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0A3B46F-577C-4FC4-A5D7-2CF964F6DA9B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613064" y="4391396"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="684000" cy="684000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="53" name="Imagen 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A815A8FD-27FF-4578-9E2E-CD6E87FB6C38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1613064" y="5118759"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>40821</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="684000" cy="684000"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="54" name="Imagen 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B48D2DC-B795-416E-AD88-50EC3AB05655}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1599457" y="5846123"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>741150</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>703050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="56" name="Imagen 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27C5E309-3A6D-036B-CD5A-5F23D1A65BC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1609725" y="8705850"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>738428</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>711214</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="58" name="Imagen 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92C20ABE-80EA-DF23-9C5C-D79FC97312B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="49720499" y="6517821"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>40821</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>40821</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>724821</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>3642</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="60" name="Imagen 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AB3C534-6C8C-714B-4C3A-C73485D30E0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1592035" y="9416142"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>738428</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>711214</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="Imagen 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75CA4A3F-E97E-3245-6492-1D89F3FD7D32}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17879785" y="1469571"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>738428</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>711214</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="65" name="Imagen 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6AC28B1-E8D8-047A-B498-B9F8FC3E5922}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId22" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17879785" y="2190750"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>27213</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>61</xdr:col>
+      <xdr:colOff>738428</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>711213</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="67" name="Imagen 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB426D85-B340-7903-0DB6-5867B3E7FF90}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="49720499" y="7238999"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>13607</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>738428</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>697607</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -781,14 +3355,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>49628</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>22413</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>735151</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>442</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>443</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -831,13 +3405,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>56030</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>11206</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>740030</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>695206</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -881,14 +3455,14 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>44824</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>22412</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>728824</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1562</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1561</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -896,6 +3470,56 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBAE795D-5AA3-4A58-83B9-571BE8EB69D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2387974" y="746312"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>44824</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>728824</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1563</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{725F7646-DBAF-42FB-9FB6-D251F09827F3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -938,57 +3562,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>728824</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>1562</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Imagen 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{725F7646-DBAF-42FB-9FB6-D251F09827F3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2387974" y="746312"/>
-          <a:ext cx="684000" cy="684000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>44824</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>22412</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>728824</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>1562</xdr:rowOff>
+      <xdr:rowOff>1561</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1031,13 +3605,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>43142</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>22412</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>711001</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>695206</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1069,6 +3643,106 @@
         <a:xfrm>
           <a:off x="1605242" y="2194112"/>
           <a:ext cx="667859" cy="672794"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>56030</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>740030</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>442</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Imagen 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FEE810C-C3CF-D779-D3ED-5558FCC7A9B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1591236" y="2846294"/>
+          <a:ext cx="684000" cy="684000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>54429</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>27214</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>738429</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>3642</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Imagen 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA0DF1C5-0547-9D6A-233D-BC336B693383}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1592036" y="3565071"/>
+          <a:ext cx="684000" cy="684000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1342,12 +4016,2902 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{260B06F4-B1DC-43BC-A49F-F95DCDB7737B}">
+  <dimension ref="A1:CV21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="18" customWidth="1"/>
+    <col min="3" max="20" width="11.7109375" style="18"/>
+    <col min="21" max="21" width="23.140625" style="18" customWidth="1"/>
+    <col min="22" max="60" width="11.7109375" style="18"/>
+    <col min="61" max="61" width="23.85546875" style="18" customWidth="1"/>
+    <col min="62" max="16384" width="11.7109375" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:100" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
+      <c r="O1" s="33"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="33"/>
+      <c r="AA1" s="33"/>
+      <c r="AB1" s="33"/>
+      <c r="AC1" s="33"/>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AI1" s="33"/>
+      <c r="AJ1" s="33"/>
+      <c r="AK1" s="33"/>
+      <c r="AL1" s="33"/>
+      <c r="AM1" s="33"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP1" s="33"/>
+      <c r="AQ1" s="33"/>
+      <c r="AR1" s="33"/>
+      <c r="AS1" s="33"/>
+      <c r="AT1" s="33"/>
+      <c r="AU1" s="33"/>
+      <c r="AV1" s="33"/>
+      <c r="AW1" s="33"/>
+      <c r="AX1" s="33"/>
+      <c r="AY1" s="33"/>
+      <c r="AZ1" s="33"/>
+      <c r="BA1" s="33"/>
+      <c r="BB1" s="33"/>
+      <c r="BC1" s="33"/>
+      <c r="BD1" s="33"/>
+      <c r="BE1" s="33"/>
+      <c r="BF1" s="33"/>
+      <c r="BG1" s="33"/>
+      <c r="BH1" s="34"/>
+      <c r="BI1" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="BJ1" s="33"/>
+      <c r="BK1" s="33"/>
+      <c r="BL1" s="33"/>
+      <c r="BM1" s="33"/>
+      <c r="BN1" s="33"/>
+      <c r="BO1" s="33"/>
+      <c r="BP1" s="33"/>
+      <c r="BQ1" s="33"/>
+      <c r="BR1" s="33"/>
+      <c r="BS1" s="33"/>
+      <c r="BT1" s="33"/>
+      <c r="BU1" s="33"/>
+      <c r="BV1" s="33"/>
+      <c r="BW1" s="33"/>
+      <c r="BX1" s="33"/>
+      <c r="BY1" s="33"/>
+      <c r="BZ1" s="33"/>
+      <c r="CA1" s="33"/>
+      <c r="CB1" s="34"/>
+      <c r="CC1" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="CD1" s="33"/>
+      <c r="CE1" s="33"/>
+      <c r="CF1" s="33"/>
+      <c r="CG1" s="33"/>
+      <c r="CH1" s="33"/>
+      <c r="CI1" s="33"/>
+      <c r="CJ1" s="33"/>
+      <c r="CK1" s="33"/>
+      <c r="CL1" s="33"/>
+      <c r="CM1" s="33"/>
+      <c r="CN1" s="33"/>
+      <c r="CO1" s="33"/>
+      <c r="CP1" s="33"/>
+      <c r="CQ1" s="33"/>
+      <c r="CR1" s="33"/>
+      <c r="CS1" s="33"/>
+      <c r="CT1" s="33"/>
+      <c r="CU1" s="33"/>
+      <c r="CV1" s="34"/>
+    </row>
+    <row r="2" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="T2" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="U2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD2" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE2" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF2" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG2" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI2" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ2" s="29"/>
+      <c r="AK2" s="29"/>
+      <c r="AL2" s="30"/>
+      <c r="AM2" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="AN2" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS2" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT2" s="29"/>
+      <c r="AU2" s="29"/>
+      <c r="AV2" s="30"/>
+      <c r="AW2" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX2" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AY2" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="AZ2" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="BA2" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="BC2" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD2" s="29"/>
+      <c r="BE2" s="29"/>
+      <c r="BF2" s="30"/>
+      <c r="BG2" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="BH2" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="BI2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ2" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM2" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN2" s="29"/>
+      <c r="BO2" s="29"/>
+      <c r="BP2" s="30"/>
+      <c r="BQ2" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="BR2" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="BS2" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="BT2" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="BU2" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="BV2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="BW2" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="BX2" s="29"/>
+      <c r="BY2" s="29"/>
+      <c r="BZ2" s="30"/>
+      <c r="CA2" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="CB2" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="CC2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="CD2" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE2" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="CF2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="CG2" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="CH2" s="29"/>
+      <c r="CI2" s="29"/>
+      <c r="CJ2" s="30"/>
+      <c r="CK2" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="CL2" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM2" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="CN2" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="CO2" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="CP2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="CQ2" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="CR2" s="29"/>
+      <c r="CS2" s="29"/>
+      <c r="CT2" s="30"/>
+      <c r="CU2" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="CV2" s="32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="V3" s="24"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="12"/>
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="12"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="12"/>
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="15"/>
+      <c r="AJ3" s="16"/>
+      <c r="AK3" s="16"/>
+      <c r="AL3" s="17"/>
+      <c r="AM3" s="12"/>
+      <c r="AN3" s="12"/>
+      <c r="AO3" s="10"/>
+      <c r="AP3" s="24"/>
+      <c r="AQ3" s="12"/>
+      <c r="AR3" s="13"/>
+      <c r="AS3" s="12"/>
+      <c r="AT3" s="14"/>
+      <c r="AU3" s="12"/>
+      <c r="AV3" s="14"/>
+      <c r="AW3" s="12"/>
+      <c r="AX3" s="13"/>
+      <c r="AY3" s="12"/>
+      <c r="AZ3" s="14"/>
+      <c r="BA3" s="12"/>
+      <c r="BB3" s="14"/>
+      <c r="BC3" s="15"/>
+      <c r="BD3" s="16"/>
+      <c r="BE3" s="16"/>
+      <c r="BF3" s="17"/>
+      <c r="BG3" s="12"/>
+      <c r="BH3" s="12"/>
+      <c r="BI3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="BJ3" s="24"/>
+      <c r="BK3" s="12"/>
+      <c r="BL3" s="13"/>
+      <c r="BM3" s="12"/>
+      <c r="BN3" s="14"/>
+      <c r="BO3" s="12"/>
+      <c r="BP3" s="14"/>
+      <c r="BQ3" s="12"/>
+      <c r="BR3" s="13"/>
+      <c r="BS3" s="12"/>
+      <c r="BT3" s="14"/>
+      <c r="BU3" s="12"/>
+      <c r="BV3" s="14"/>
+      <c r="BW3" s="15"/>
+      <c r="BX3" s="16"/>
+      <c r="BY3" s="16"/>
+      <c r="BZ3" s="17"/>
+      <c r="CA3" s="12"/>
+      <c r="CB3" s="12"/>
+      <c r="CC3" s="10"/>
+      <c r="CD3" s="24"/>
+      <c r="CE3" s="12"/>
+      <c r="CF3" s="13"/>
+      <c r="CG3" s="12"/>
+      <c r="CH3" s="14"/>
+      <c r="CI3" s="12"/>
+      <c r="CJ3" s="14"/>
+      <c r="CK3" s="12"/>
+      <c r="CL3" s="13"/>
+      <c r="CM3" s="12"/>
+      <c r="CN3" s="14"/>
+      <c r="CO3" s="12"/>
+      <c r="CP3" s="14"/>
+      <c r="CQ3" s="15"/>
+      <c r="CR3" s="16"/>
+      <c r="CS3" s="16"/>
+      <c r="CT3" s="17"/>
+      <c r="CU3" s="12"/>
+      <c r="CV3" s="12"/>
+    </row>
+    <row r="4" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+      <c r="U4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="V4" s="24"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="12"/>
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="12"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="12"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="12"/>
+      <c r="AF4" s="14"/>
+      <c r="AG4" s="12"/>
+      <c r="AH4" s="14"/>
+      <c r="AI4" s="15"/>
+      <c r="AJ4" s="16"/>
+      <c r="AK4" s="16"/>
+      <c r="AL4" s="17"/>
+      <c r="AM4" s="12"/>
+      <c r="AN4" s="12"/>
+      <c r="AO4" s="10"/>
+      <c r="AP4" s="24"/>
+      <c r="AQ4" s="12"/>
+      <c r="AR4" s="13"/>
+      <c r="AS4" s="12"/>
+      <c r="AT4" s="14"/>
+      <c r="AU4" s="12"/>
+      <c r="AV4" s="14"/>
+      <c r="AW4" s="12"/>
+      <c r="AX4" s="13"/>
+      <c r="AY4" s="12"/>
+      <c r="AZ4" s="14"/>
+      <c r="BA4" s="12"/>
+      <c r="BB4" s="14"/>
+      <c r="BC4" s="15"/>
+      <c r="BD4" s="16"/>
+      <c r="BE4" s="16"/>
+      <c r="BF4" s="17"/>
+      <c r="BG4" s="12"/>
+      <c r="BH4" s="12"/>
+      <c r="BI4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="BJ4" s="24"/>
+      <c r="BK4" s="12"/>
+      <c r="BL4" s="13"/>
+      <c r="BM4" s="12"/>
+      <c r="BN4" s="14"/>
+      <c r="BO4" s="12"/>
+      <c r="BP4" s="14"/>
+      <c r="BQ4" s="12"/>
+      <c r="BR4" s="13"/>
+      <c r="BS4" s="12"/>
+      <c r="BT4" s="14"/>
+      <c r="BU4" s="12"/>
+      <c r="BV4" s="14"/>
+      <c r="BW4" s="15"/>
+      <c r="BX4" s="16"/>
+      <c r="BY4" s="16"/>
+      <c r="BZ4" s="17"/>
+      <c r="CA4" s="12"/>
+      <c r="CB4" s="12"/>
+      <c r="CC4" s="10"/>
+      <c r="CD4" s="24"/>
+      <c r="CE4" s="12"/>
+      <c r="CF4" s="13"/>
+      <c r="CG4" s="12"/>
+      <c r="CH4" s="14"/>
+      <c r="CI4" s="12"/>
+      <c r="CJ4" s="14"/>
+      <c r="CK4" s="12"/>
+      <c r="CL4" s="13"/>
+      <c r="CM4" s="12"/>
+      <c r="CN4" s="14"/>
+      <c r="CO4" s="12"/>
+      <c r="CP4" s="14"/>
+      <c r="CQ4" s="15"/>
+      <c r="CR4" s="16"/>
+      <c r="CS4" s="16"/>
+      <c r="CT4" s="17"/>
+      <c r="CU4" s="12"/>
+      <c r="CV4" s="12"/>
+    </row>
+    <row r="5" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="12"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="12"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="12"/>
+      <c r="AB5" s="14"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="12"/>
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="12"/>
+      <c r="AH5" s="14"/>
+      <c r="AI5" s="15"/>
+      <c r="AJ5" s="16"/>
+      <c r="AK5" s="16"/>
+      <c r="AL5" s="17"/>
+      <c r="AM5" s="12"/>
+      <c r="AN5" s="12"/>
+      <c r="AO5" s="10"/>
+      <c r="AP5" s="24"/>
+      <c r="AQ5" s="12"/>
+      <c r="AR5" s="13"/>
+      <c r="AS5" s="12"/>
+      <c r="AT5" s="14"/>
+      <c r="AU5" s="12"/>
+      <c r="AV5" s="14"/>
+      <c r="AW5" s="12"/>
+      <c r="AX5" s="13"/>
+      <c r="AY5" s="12"/>
+      <c r="AZ5" s="14"/>
+      <c r="BA5" s="12"/>
+      <c r="BB5" s="14"/>
+      <c r="BC5" s="15"/>
+      <c r="BD5" s="16"/>
+      <c r="BE5" s="16"/>
+      <c r="BF5" s="17"/>
+      <c r="BG5" s="12"/>
+      <c r="BH5" s="12"/>
+      <c r="BI5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="BJ5" s="24"/>
+      <c r="BK5" s="12"/>
+      <c r="BL5" s="13"/>
+      <c r="BM5" s="12"/>
+      <c r="BN5" s="14"/>
+      <c r="BO5" s="12"/>
+      <c r="BP5" s="14"/>
+      <c r="BQ5" s="12"/>
+      <c r="BR5" s="13"/>
+      <c r="BS5" s="12"/>
+      <c r="BT5" s="14"/>
+      <c r="BU5" s="12"/>
+      <c r="BV5" s="14"/>
+      <c r="BW5" s="15"/>
+      <c r="BX5" s="16"/>
+      <c r="BY5" s="16"/>
+      <c r="BZ5" s="17"/>
+      <c r="CA5" s="12"/>
+      <c r="CB5" s="12"/>
+      <c r="CC5" s="10"/>
+      <c r="CD5" s="24"/>
+      <c r="CE5" s="12"/>
+      <c r="CF5" s="13"/>
+      <c r="CG5" s="12"/>
+      <c r="CH5" s="14"/>
+      <c r="CI5" s="12"/>
+      <c r="CJ5" s="14"/>
+      <c r="CK5" s="12"/>
+      <c r="CL5" s="13"/>
+      <c r="CM5" s="12"/>
+      <c r="CN5" s="14"/>
+      <c r="CO5" s="12"/>
+      <c r="CP5" s="14"/>
+      <c r="CQ5" s="15"/>
+      <c r="CR5" s="16"/>
+      <c r="CS5" s="16"/>
+      <c r="CT5" s="17"/>
+      <c r="CU5" s="12"/>
+      <c r="CV5" s="12"/>
+    </row>
+    <row r="6" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="24"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="12"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="13"/>
+      <c r="AE6" s="12"/>
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="12"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="15"/>
+      <c r="AJ6" s="16"/>
+      <c r="AK6" s="16"/>
+      <c r="AL6" s="17"/>
+      <c r="AM6" s="12"/>
+      <c r="AN6" s="12"/>
+      <c r="AO6" s="10"/>
+      <c r="AP6" s="24"/>
+      <c r="AQ6" s="12"/>
+      <c r="AR6" s="13"/>
+      <c r="AS6" s="12"/>
+      <c r="AT6" s="14"/>
+      <c r="AU6" s="12"/>
+      <c r="AV6" s="14"/>
+      <c r="AW6" s="12"/>
+      <c r="AX6" s="13"/>
+      <c r="AY6" s="12"/>
+      <c r="AZ6" s="14"/>
+      <c r="BA6" s="12"/>
+      <c r="BB6" s="14"/>
+      <c r="BC6" s="15"/>
+      <c r="BD6" s="16"/>
+      <c r="BE6" s="16"/>
+      <c r="BF6" s="17"/>
+      <c r="BG6" s="12"/>
+      <c r="BH6" s="12"/>
+      <c r="BI6" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ6" s="24"/>
+      <c r="BK6" s="12"/>
+      <c r="BL6" s="13"/>
+      <c r="BM6" s="12"/>
+      <c r="BN6" s="14"/>
+      <c r="BO6" s="12"/>
+      <c r="BP6" s="14"/>
+      <c r="BQ6" s="12"/>
+      <c r="BR6" s="13"/>
+      <c r="BS6" s="12"/>
+      <c r="BT6" s="14"/>
+      <c r="BU6" s="12"/>
+      <c r="BV6" s="14"/>
+      <c r="BW6" s="15"/>
+      <c r="BX6" s="16"/>
+      <c r="BY6" s="16"/>
+      <c r="BZ6" s="17"/>
+      <c r="CA6" s="12"/>
+      <c r="CB6" s="12"/>
+      <c r="CC6" s="10"/>
+      <c r="CD6" s="24"/>
+      <c r="CE6" s="12"/>
+      <c r="CF6" s="13"/>
+      <c r="CG6" s="12"/>
+      <c r="CH6" s="14"/>
+      <c r="CI6" s="12"/>
+      <c r="CJ6" s="14"/>
+      <c r="CK6" s="12"/>
+      <c r="CL6" s="13"/>
+      <c r="CM6" s="12"/>
+      <c r="CN6" s="14"/>
+      <c r="CO6" s="12"/>
+      <c r="CP6" s="14"/>
+      <c r="CQ6" s="15"/>
+      <c r="CR6" s="16"/>
+      <c r="CS6" s="16"/>
+      <c r="CT6" s="17"/>
+      <c r="CU6" s="12"/>
+      <c r="CV6" s="12"/>
+    </row>
+    <row r="7" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="12"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="12"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="12"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="15"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="12"/>
+      <c r="AN7" s="12"/>
+      <c r="AO7" s="10"/>
+      <c r="AP7" s="24"/>
+      <c r="AQ7" s="12"/>
+      <c r="AR7" s="13"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="14"/>
+      <c r="AU7" s="12"/>
+      <c r="AV7" s="14"/>
+      <c r="AW7" s="12"/>
+      <c r="AX7" s="13"/>
+      <c r="AY7" s="12"/>
+      <c r="AZ7" s="14"/>
+      <c r="BA7" s="12"/>
+      <c r="BB7" s="14"/>
+      <c r="BC7" s="15"/>
+      <c r="BD7" s="16"/>
+      <c r="BE7" s="16"/>
+      <c r="BF7" s="17"/>
+      <c r="BG7" s="12"/>
+      <c r="BH7" s="12"/>
+      <c r="BI7" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="BJ7" s="24"/>
+      <c r="BK7" s="12"/>
+      <c r="BL7" s="13"/>
+      <c r="BM7" s="12"/>
+      <c r="BN7" s="14"/>
+      <c r="BO7" s="12"/>
+      <c r="BP7" s="14"/>
+      <c r="BQ7" s="12"/>
+      <c r="BR7" s="13"/>
+      <c r="BS7" s="12"/>
+      <c r="BT7" s="14"/>
+      <c r="BU7" s="12"/>
+      <c r="BV7" s="14"/>
+      <c r="BW7" s="15"/>
+      <c r="BX7" s="16"/>
+      <c r="BY7" s="16"/>
+      <c r="BZ7" s="17"/>
+      <c r="CA7" s="12"/>
+      <c r="CB7" s="12"/>
+      <c r="CC7" s="10"/>
+      <c r="CD7" s="24"/>
+      <c r="CE7" s="12"/>
+      <c r="CF7" s="13"/>
+      <c r="CG7" s="12"/>
+      <c r="CH7" s="14"/>
+      <c r="CI7" s="12"/>
+      <c r="CJ7" s="14"/>
+      <c r="CK7" s="12"/>
+      <c r="CL7" s="13"/>
+      <c r="CM7" s="12"/>
+      <c r="CN7" s="14"/>
+      <c r="CO7" s="12"/>
+      <c r="CP7" s="14"/>
+      <c r="CQ7" s="15"/>
+      <c r="CR7" s="16"/>
+      <c r="CS7" s="16"/>
+      <c r="CT7" s="17"/>
+      <c r="CU7" s="12"/>
+      <c r="CV7" s="12"/>
+    </row>
+    <row r="8" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="24"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="12"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="12"/>
+      <c r="Z8" s="14"/>
+      <c r="AA8" s="12"/>
+      <c r="AB8" s="14"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="13"/>
+      <c r="AE8" s="12"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="12"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="15"/>
+      <c r="AJ8" s="16"/>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="10"/>
+      <c r="AP8" s="24"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="13"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="14"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="14"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="13"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="14"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="14"/>
+      <c r="BC8" s="15"/>
+      <c r="BD8" s="16"/>
+      <c r="BE8" s="16"/>
+      <c r="BF8" s="17"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+      <c r="BI8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="BJ8" s="24"/>
+      <c r="BK8" s="12"/>
+      <c r="BL8" s="13"/>
+      <c r="BM8" s="12"/>
+      <c r="BN8" s="14"/>
+      <c r="BO8" s="12"/>
+      <c r="BP8" s="14"/>
+      <c r="BQ8" s="12"/>
+      <c r="BR8" s="13"/>
+      <c r="BS8" s="12"/>
+      <c r="BT8" s="14"/>
+      <c r="BU8" s="12"/>
+      <c r="BV8" s="14"/>
+      <c r="BW8" s="15"/>
+      <c r="BX8" s="16"/>
+      <c r="BY8" s="16"/>
+      <c r="BZ8" s="17"/>
+      <c r="CA8" s="12"/>
+      <c r="CB8" s="12"/>
+      <c r="CC8" s="10"/>
+      <c r="CD8" s="24"/>
+      <c r="CE8" s="12"/>
+      <c r="CF8" s="13"/>
+      <c r="CG8" s="12"/>
+      <c r="CH8" s="14"/>
+      <c r="CI8" s="12"/>
+      <c r="CJ8" s="14"/>
+      <c r="CK8" s="12"/>
+      <c r="CL8" s="13"/>
+      <c r="CM8" s="12"/>
+      <c r="CN8" s="14"/>
+      <c r="CO8" s="12"/>
+      <c r="CP8" s="14"/>
+      <c r="CQ8" s="15"/>
+      <c r="CR8" s="16"/>
+      <c r="CS8" s="16"/>
+      <c r="CT8" s="17"/>
+      <c r="CU8" s="12"/>
+      <c r="CV8" s="12"/>
+    </row>
+    <row r="9" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="12"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="12"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="12"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="12"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="12"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="15"/>
+      <c r="AJ9" s="16"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="10"/>
+      <c r="AP9" s="24"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="13"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="14"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="13"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="14"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="15"/>
+      <c r="BD9" s="16"/>
+      <c r="BE9" s="16"/>
+      <c r="BF9" s="17"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+      <c r="BI9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="BJ9" s="24"/>
+      <c r="BK9" s="12"/>
+      <c r="BL9" s="13"/>
+      <c r="BM9" s="12"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="12"/>
+      <c r="BP9" s="14"/>
+      <c r="BQ9" s="12"/>
+      <c r="BR9" s="13"/>
+      <c r="BS9" s="12"/>
+      <c r="BT9" s="14"/>
+      <c r="BU9" s="12"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="15"/>
+      <c r="BX9" s="16"/>
+      <c r="BY9" s="16"/>
+      <c r="BZ9" s="17"/>
+      <c r="CA9" s="12"/>
+      <c r="CB9" s="12"/>
+      <c r="CC9" s="10"/>
+      <c r="CD9" s="24"/>
+      <c r="CE9" s="12"/>
+      <c r="CF9" s="13"/>
+      <c r="CG9" s="12"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="12"/>
+      <c r="CJ9" s="14"/>
+      <c r="CK9" s="12"/>
+      <c r="CL9" s="13"/>
+      <c r="CM9" s="12"/>
+      <c r="CN9" s="14"/>
+      <c r="CO9" s="12"/>
+      <c r="CP9" s="14"/>
+      <c r="CQ9" s="15"/>
+      <c r="CR9" s="16"/>
+      <c r="CS9" s="16"/>
+      <c r="CT9" s="17"/>
+      <c r="CU9" s="12"/>
+      <c r="CV9" s="12"/>
+    </row>
+    <row r="10" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="12"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="12"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="12"/>
+      <c r="AF10" s="14"/>
+      <c r="AG10" s="12"/>
+      <c r="AH10" s="14"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="16"/>
+      <c r="AK10" s="16"/>
+      <c r="AL10" s="17"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="10"/>
+      <c r="AP10" s="24"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="13"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="14"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="14"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="13"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="14"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="14"/>
+      <c r="BC10" s="15"/>
+      <c r="BD10" s="16"/>
+      <c r="BE10" s="16"/>
+      <c r="BF10" s="17"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+      <c r="BI10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="BJ10" s="24"/>
+      <c r="BK10" s="12"/>
+      <c r="BL10" s="13"/>
+      <c r="BM10" s="12"/>
+      <c r="BN10" s="14"/>
+      <c r="BO10" s="12"/>
+      <c r="BP10" s="14"/>
+      <c r="BQ10" s="12"/>
+      <c r="BR10" s="13"/>
+      <c r="BS10" s="12"/>
+      <c r="BT10" s="14"/>
+      <c r="BU10" s="12"/>
+      <c r="BV10" s="14"/>
+      <c r="BW10" s="15"/>
+      <c r="BX10" s="16"/>
+      <c r="BY10" s="16"/>
+      <c r="BZ10" s="17"/>
+      <c r="CA10" s="12"/>
+      <c r="CB10" s="12"/>
+      <c r="CC10" s="10"/>
+      <c r="CD10" s="24"/>
+      <c r="CE10" s="12"/>
+      <c r="CF10" s="13"/>
+      <c r="CG10" s="12"/>
+      <c r="CH10" s="14"/>
+      <c r="CI10" s="12"/>
+      <c r="CJ10" s="14"/>
+      <c r="CK10" s="12"/>
+      <c r="CL10" s="13"/>
+      <c r="CM10" s="12"/>
+      <c r="CN10" s="14"/>
+      <c r="CO10" s="12"/>
+      <c r="CP10" s="14"/>
+      <c r="CQ10" s="15"/>
+      <c r="CR10" s="16"/>
+      <c r="CS10" s="16"/>
+      <c r="CT10" s="17"/>
+      <c r="CU10" s="12"/>
+      <c r="CV10" s="12"/>
+    </row>
+    <row r="11" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="24"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="12"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="12"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="12"/>
+      <c r="AF11" s="14"/>
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="14"/>
+      <c r="AI11" s="15"/>
+      <c r="AJ11" s="16"/>
+      <c r="AK11" s="16"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="10"/>
+      <c r="AP11" s="24"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="13"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="14"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="14"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="13"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="14"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="14"/>
+      <c r="BC11" s="15"/>
+      <c r="BD11" s="16"/>
+      <c r="BE11" s="16"/>
+      <c r="BF11" s="17"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+      <c r="BI11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="BJ11" s="24"/>
+      <c r="BK11" s="12"/>
+      <c r="BL11" s="13"/>
+      <c r="BM11" s="12"/>
+      <c r="BN11" s="14"/>
+      <c r="BO11" s="12"/>
+      <c r="BP11" s="14"/>
+      <c r="BQ11" s="12"/>
+      <c r="BR11" s="13"/>
+      <c r="BS11" s="12"/>
+      <c r="BT11" s="14"/>
+      <c r="BU11" s="12"/>
+      <c r="BV11" s="14"/>
+      <c r="BW11" s="15"/>
+      <c r="BX11" s="16"/>
+      <c r="BY11" s="16"/>
+      <c r="BZ11" s="17"/>
+      <c r="CA11" s="12"/>
+      <c r="CB11" s="12"/>
+      <c r="CC11" s="10"/>
+      <c r="CD11" s="24"/>
+      <c r="CE11" s="12"/>
+      <c r="CF11" s="13"/>
+      <c r="CG11" s="12"/>
+      <c r="CH11" s="14"/>
+      <c r="CI11" s="12"/>
+      <c r="CJ11" s="14"/>
+      <c r="CK11" s="12"/>
+      <c r="CL11" s="13"/>
+      <c r="CM11" s="12"/>
+      <c r="CN11" s="14"/>
+      <c r="CO11" s="12"/>
+      <c r="CP11" s="14"/>
+      <c r="CQ11" s="15"/>
+      <c r="CR11" s="16"/>
+      <c r="CS11" s="16"/>
+      <c r="CT11" s="17"/>
+      <c r="CU11" s="12"/>
+      <c r="CV11" s="12"/>
+    </row>
+    <row r="12" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="12"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="12"/>
+      <c r="Z12" s="14"/>
+      <c r="AA12" s="12"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="12"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="12"/>
+      <c r="AF12" s="14"/>
+      <c r="AG12" s="12"/>
+      <c r="AH12" s="14"/>
+      <c r="AI12" s="15"/>
+      <c r="AJ12" s="16"/>
+      <c r="AK12" s="16"/>
+      <c r="AL12" s="17"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="10"/>
+      <c r="AP12" s="24"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="13"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="14"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="14"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="13"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="14"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="14"/>
+      <c r="BC12" s="15"/>
+      <c r="BD12" s="16"/>
+      <c r="BE12" s="16"/>
+      <c r="BF12" s="17"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+      <c r="BI12" s="10"/>
+      <c r="BJ12" s="24"/>
+      <c r="BK12" s="12"/>
+      <c r="BL12" s="13"/>
+      <c r="BM12" s="12"/>
+      <c r="BN12" s="14"/>
+      <c r="BO12" s="12"/>
+      <c r="BP12" s="14"/>
+      <c r="BQ12" s="12"/>
+      <c r="BR12" s="13"/>
+      <c r="BS12" s="12"/>
+      <c r="BT12" s="14"/>
+      <c r="BU12" s="12"/>
+      <c r="BV12" s="14"/>
+      <c r="BW12" s="15"/>
+      <c r="BX12" s="16"/>
+      <c r="BY12" s="16"/>
+      <c r="BZ12" s="17"/>
+      <c r="CA12" s="12"/>
+      <c r="CB12" s="12"/>
+      <c r="CC12" s="10"/>
+      <c r="CD12" s="24"/>
+      <c r="CE12" s="12"/>
+      <c r="CF12" s="13"/>
+      <c r="CG12" s="12"/>
+      <c r="CH12" s="14"/>
+      <c r="CI12" s="12"/>
+      <c r="CJ12" s="14"/>
+      <c r="CK12" s="12"/>
+      <c r="CL12" s="13"/>
+      <c r="CM12" s="12"/>
+      <c r="CN12" s="14"/>
+      <c r="CO12" s="12"/>
+      <c r="CP12" s="14"/>
+      <c r="CQ12" s="15"/>
+      <c r="CR12" s="16"/>
+      <c r="CS12" s="16"/>
+      <c r="CT12" s="17"/>
+      <c r="CU12" s="12"/>
+      <c r="CV12" s="12"/>
+    </row>
+    <row r="13" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="12"/>
+      <c r="AB13" s="14"/>
+      <c r="AC13" s="12"/>
+      <c r="AD13" s="13"/>
+      <c r="AE13" s="12"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="12"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="15"/>
+      <c r="AJ13" s="16"/>
+      <c r="AK13" s="16"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="10"/>
+      <c r="AP13" s="24"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="13"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="14"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="14"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="13"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="14"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="14"/>
+      <c r="BC13" s="15"/>
+      <c r="BD13" s="16"/>
+      <c r="BE13" s="16"/>
+      <c r="BF13" s="17"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+      <c r="BI13" s="10"/>
+      <c r="BJ13" s="24"/>
+      <c r="BK13" s="12"/>
+      <c r="BL13" s="13"/>
+      <c r="BM13" s="12"/>
+      <c r="BN13" s="14"/>
+      <c r="BO13" s="12"/>
+      <c r="BP13" s="14"/>
+      <c r="BQ13" s="12"/>
+      <c r="BR13" s="13"/>
+      <c r="BS13" s="12"/>
+      <c r="BT13" s="14"/>
+      <c r="BU13" s="12"/>
+      <c r="BV13" s="14"/>
+      <c r="BW13" s="15"/>
+      <c r="BX13" s="16"/>
+      <c r="BY13" s="16"/>
+      <c r="BZ13" s="17"/>
+      <c r="CA13" s="12"/>
+      <c r="CB13" s="12"/>
+      <c r="CC13" s="10"/>
+      <c r="CD13" s="24"/>
+      <c r="CE13" s="12"/>
+      <c r="CF13" s="13"/>
+      <c r="CG13" s="12"/>
+      <c r="CH13" s="14"/>
+      <c r="CI13" s="12"/>
+      <c r="CJ13" s="14"/>
+      <c r="CK13" s="12"/>
+      <c r="CL13" s="13"/>
+      <c r="CM13" s="12"/>
+      <c r="CN13" s="14"/>
+      <c r="CO13" s="12"/>
+      <c r="CP13" s="14"/>
+      <c r="CQ13" s="15"/>
+      <c r="CR13" s="16"/>
+      <c r="CS13" s="16"/>
+      <c r="CT13" s="17"/>
+      <c r="CU13" s="12"/>
+      <c r="CV13" s="12"/>
+    </row>
+    <row r="14" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="14"/>
+      <c r="AA14" s="12"/>
+      <c r="AB14" s="14"/>
+      <c r="AC14" s="12"/>
+      <c r="AD14" s="13"/>
+      <c r="AE14" s="12"/>
+      <c r="AF14" s="14"/>
+      <c r="AG14" s="12"/>
+      <c r="AH14" s="14"/>
+      <c r="AI14" s="15"/>
+      <c r="AJ14" s="16"/>
+      <c r="AK14" s="16"/>
+      <c r="AL14" s="17"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="10"/>
+      <c r="AP14" s="24"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="13"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="14"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="14"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="13"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="14"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="14"/>
+      <c r="BC14" s="15"/>
+      <c r="BD14" s="16"/>
+      <c r="BE14" s="16"/>
+      <c r="BF14" s="17"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+      <c r="BI14" s="10"/>
+      <c r="BJ14" s="24"/>
+      <c r="BK14" s="12"/>
+      <c r="BL14" s="13"/>
+      <c r="BM14" s="12"/>
+      <c r="BN14" s="14"/>
+      <c r="BO14" s="12"/>
+      <c r="BP14" s="14"/>
+      <c r="BQ14" s="12"/>
+      <c r="BR14" s="13"/>
+      <c r="BS14" s="12"/>
+      <c r="BT14" s="14"/>
+      <c r="BU14" s="12"/>
+      <c r="BV14" s="14"/>
+      <c r="BW14" s="15"/>
+      <c r="BX14" s="16"/>
+      <c r="BY14" s="16"/>
+      <c r="BZ14" s="17"/>
+      <c r="CA14" s="12"/>
+      <c r="CB14" s="12"/>
+      <c r="CC14" s="10"/>
+      <c r="CD14" s="24"/>
+      <c r="CE14" s="12"/>
+      <c r="CF14" s="13"/>
+      <c r="CG14" s="12"/>
+      <c r="CH14" s="14"/>
+      <c r="CI14" s="12"/>
+      <c r="CJ14" s="14"/>
+      <c r="CK14" s="12"/>
+      <c r="CL14" s="13"/>
+      <c r="CM14" s="12"/>
+      <c r="CN14" s="14"/>
+      <c r="CO14" s="12"/>
+      <c r="CP14" s="14"/>
+      <c r="CQ14" s="15"/>
+      <c r="CR14" s="16"/>
+      <c r="CS14" s="16"/>
+      <c r="CT14" s="17"/>
+      <c r="CU14" s="12"/>
+      <c r="CV14" s="12"/>
+    </row>
+    <row r="15" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="14"/>
+      <c r="AA15" s="12"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="13"/>
+      <c r="AE15" s="12"/>
+      <c r="AF15" s="14"/>
+      <c r="AG15" s="12"/>
+      <c r="AH15" s="14"/>
+      <c r="AI15" s="15"/>
+      <c r="AJ15" s="16"/>
+      <c r="AK15" s="16"/>
+      <c r="AL15" s="17"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="10"/>
+      <c r="AP15" s="24"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="13"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="14"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="14"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="13"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="14"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="14"/>
+      <c r="BC15" s="15"/>
+      <c r="BD15" s="16"/>
+      <c r="BE15" s="16"/>
+      <c r="BF15" s="17"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+      <c r="BI15" s="10"/>
+      <c r="BJ15" s="24"/>
+      <c r="BK15" s="12"/>
+      <c r="BL15" s="13"/>
+      <c r="BM15" s="12"/>
+      <c r="BN15" s="14"/>
+      <c r="BO15" s="12"/>
+      <c r="BP15" s="14"/>
+      <c r="BQ15" s="12"/>
+      <c r="BR15" s="13"/>
+      <c r="BS15" s="12"/>
+      <c r="BT15" s="14"/>
+      <c r="BU15" s="12"/>
+      <c r="BV15" s="14"/>
+      <c r="BW15" s="15"/>
+      <c r="BX15" s="16"/>
+      <c r="BY15" s="16"/>
+      <c r="BZ15" s="17"/>
+      <c r="CA15" s="12"/>
+      <c r="CB15" s="12"/>
+      <c r="CC15" s="10"/>
+      <c r="CD15" s="24"/>
+      <c r="CE15" s="12"/>
+      <c r="CF15" s="13"/>
+      <c r="CG15" s="12"/>
+      <c r="CH15" s="14"/>
+      <c r="CI15" s="12"/>
+      <c r="CJ15" s="14"/>
+      <c r="CK15" s="12"/>
+      <c r="CL15" s="13"/>
+      <c r="CM15" s="12"/>
+      <c r="CN15" s="14"/>
+      <c r="CO15" s="12"/>
+      <c r="CP15" s="14"/>
+      <c r="CQ15" s="15"/>
+      <c r="CR15" s="16"/>
+      <c r="CS15" s="16"/>
+      <c r="CT15" s="17"/>
+      <c r="CU15" s="12"/>
+      <c r="CV15" s="12"/>
+    </row>
+    <row r="16" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="12"/>
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="12"/>
+      <c r="AD16" s="13"/>
+      <c r="AE16" s="12"/>
+      <c r="AF16" s="14"/>
+      <c r="AG16" s="12"/>
+      <c r="AH16" s="14"/>
+      <c r="AI16" s="15"/>
+      <c r="AJ16" s="16"/>
+      <c r="AK16" s="16"/>
+      <c r="AL16" s="17"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="10"/>
+      <c r="AP16" s="24"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="13"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="14"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="14"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="13"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="14"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="14"/>
+      <c r="BC16" s="15"/>
+      <c r="BD16" s="16"/>
+      <c r="BE16" s="16"/>
+      <c r="BF16" s="17"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+      <c r="BI16" s="10"/>
+      <c r="BJ16" s="24"/>
+      <c r="BK16" s="12"/>
+      <c r="BL16" s="13"/>
+      <c r="BM16" s="12"/>
+      <c r="BN16" s="14"/>
+      <c r="BO16" s="12"/>
+      <c r="BP16" s="14"/>
+      <c r="BQ16" s="12"/>
+      <c r="BR16" s="13"/>
+      <c r="BS16" s="12"/>
+      <c r="BT16" s="14"/>
+      <c r="BU16" s="12"/>
+      <c r="BV16" s="14"/>
+      <c r="BW16" s="15"/>
+      <c r="BX16" s="16"/>
+      <c r="BY16" s="16"/>
+      <c r="BZ16" s="17"/>
+      <c r="CA16" s="12"/>
+      <c r="CB16" s="12"/>
+      <c r="CC16" s="10"/>
+      <c r="CD16" s="24"/>
+      <c r="CE16" s="12"/>
+      <c r="CF16" s="13"/>
+      <c r="CG16" s="12"/>
+      <c r="CH16" s="14"/>
+      <c r="CI16" s="12"/>
+      <c r="CJ16" s="14"/>
+      <c r="CK16" s="12"/>
+      <c r="CL16" s="13"/>
+      <c r="CM16" s="12"/>
+      <c r="CN16" s="14"/>
+      <c r="CO16" s="12"/>
+      <c r="CP16" s="14"/>
+      <c r="CQ16" s="15"/>
+      <c r="CR16" s="16"/>
+      <c r="CS16" s="16"/>
+      <c r="CT16" s="17"/>
+      <c r="CU16" s="12"/>
+      <c r="CV16" s="12"/>
+    </row>
+    <row r="17" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="12"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="12"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="12"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="12"/>
+      <c r="AF17" s="14"/>
+      <c r="AG17" s="12"/>
+      <c r="AH17" s="14"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="17"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="10"/>
+      <c r="AP17" s="24"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="13"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="14"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="14"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="13"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="14"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="14"/>
+      <c r="BC17" s="15"/>
+      <c r="BD17" s="16"/>
+      <c r="BE17" s="16"/>
+      <c r="BF17" s="17"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+      <c r="BI17" s="10"/>
+      <c r="BJ17" s="24"/>
+      <c r="BK17" s="12"/>
+      <c r="BL17" s="13"/>
+      <c r="BM17" s="12"/>
+      <c r="BN17" s="14"/>
+      <c r="BO17" s="12"/>
+      <c r="BP17" s="14"/>
+      <c r="BQ17" s="12"/>
+      <c r="BR17" s="13"/>
+      <c r="BS17" s="12"/>
+      <c r="BT17" s="14"/>
+      <c r="BU17" s="12"/>
+      <c r="BV17" s="14"/>
+      <c r="BW17" s="15"/>
+      <c r="BX17" s="16"/>
+      <c r="BY17" s="16"/>
+      <c r="BZ17" s="17"/>
+      <c r="CA17" s="12"/>
+      <c r="CB17" s="12"/>
+      <c r="CC17" s="10"/>
+      <c r="CD17" s="24"/>
+      <c r="CE17" s="12"/>
+      <c r="CF17" s="13"/>
+      <c r="CG17" s="12"/>
+      <c r="CH17" s="14"/>
+      <c r="CI17" s="12"/>
+      <c r="CJ17" s="14"/>
+      <c r="CK17" s="12"/>
+      <c r="CL17" s="13"/>
+      <c r="CM17" s="12"/>
+      <c r="CN17" s="14"/>
+      <c r="CO17" s="12"/>
+      <c r="CP17" s="14"/>
+      <c r="CQ17" s="15"/>
+      <c r="CR17" s="16"/>
+      <c r="CS17" s="16"/>
+      <c r="CT17" s="17"/>
+      <c r="CU17" s="12"/>
+      <c r="CV17" s="12"/>
+    </row>
+    <row r="18" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="24"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="12"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="12"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="12"/>
+      <c r="AF18" s="14"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="14"/>
+      <c r="AI18" s="15"/>
+      <c r="AJ18" s="16"/>
+      <c r="AK18" s="16"/>
+      <c r="AL18" s="17"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="10"/>
+      <c r="AP18" s="24"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="13"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="14"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="14"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="13"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="14"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="14"/>
+      <c r="BC18" s="15"/>
+      <c r="BD18" s="16"/>
+      <c r="BE18" s="16"/>
+      <c r="BF18" s="17"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+      <c r="BI18" s="10"/>
+      <c r="BJ18" s="24"/>
+      <c r="BK18" s="12"/>
+      <c r="BL18" s="13"/>
+      <c r="BM18" s="12"/>
+      <c r="BN18" s="14"/>
+      <c r="BO18" s="12"/>
+      <c r="BP18" s="14"/>
+      <c r="BQ18" s="12"/>
+      <c r="BR18" s="13"/>
+      <c r="BS18" s="12"/>
+      <c r="BT18" s="14"/>
+      <c r="BU18" s="12"/>
+      <c r="BV18" s="14"/>
+      <c r="BW18" s="15"/>
+      <c r="BX18" s="16"/>
+      <c r="BY18" s="16"/>
+      <c r="BZ18" s="17"/>
+      <c r="CA18" s="12"/>
+      <c r="CB18" s="12"/>
+      <c r="CC18" s="10"/>
+      <c r="CD18" s="24"/>
+      <c r="CE18" s="12"/>
+      <c r="CF18" s="13"/>
+      <c r="CG18" s="12"/>
+      <c r="CH18" s="14"/>
+      <c r="CI18" s="12"/>
+      <c r="CJ18" s="14"/>
+      <c r="CK18" s="12"/>
+      <c r="CL18" s="13"/>
+      <c r="CM18" s="12"/>
+      <c r="CN18" s="14"/>
+      <c r="CO18" s="12"/>
+      <c r="CP18" s="14"/>
+      <c r="CQ18" s="15"/>
+      <c r="CR18" s="16"/>
+      <c r="CS18" s="16"/>
+      <c r="CT18" s="17"/>
+      <c r="CU18" s="12"/>
+      <c r="CV18" s="12"/>
+    </row>
+    <row r="19" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="24"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="14"/>
+      <c r="AA19" s="12"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="12"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="12"/>
+      <c r="AF19" s="14"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="14"/>
+      <c r="AI19" s="15"/>
+      <c r="AJ19" s="16"/>
+      <c r="AK19" s="16"/>
+      <c r="AL19" s="17"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="10"/>
+      <c r="AP19" s="24"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="13"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="14"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="14"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="13"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="14"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="14"/>
+      <c r="BC19" s="15"/>
+      <c r="BD19" s="16"/>
+      <c r="BE19" s="16"/>
+      <c r="BF19" s="17"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+      <c r="BI19" s="10"/>
+      <c r="BJ19" s="24"/>
+      <c r="BK19" s="12"/>
+      <c r="BL19" s="13"/>
+      <c r="BM19" s="12"/>
+      <c r="BN19" s="14"/>
+      <c r="BO19" s="12"/>
+      <c r="BP19" s="14"/>
+      <c r="BQ19" s="12"/>
+      <c r="BR19" s="13"/>
+      <c r="BS19" s="12"/>
+      <c r="BT19" s="14"/>
+      <c r="BU19" s="12"/>
+      <c r="BV19" s="14"/>
+      <c r="BW19" s="15"/>
+      <c r="BX19" s="16"/>
+      <c r="BY19" s="16"/>
+      <c r="BZ19" s="17"/>
+      <c r="CA19" s="12"/>
+      <c r="CB19" s="12"/>
+      <c r="CC19" s="10"/>
+      <c r="CD19" s="24"/>
+      <c r="CE19" s="12"/>
+      <c r="CF19" s="13"/>
+      <c r="CG19" s="12"/>
+      <c r="CH19" s="14"/>
+      <c r="CI19" s="12"/>
+      <c r="CJ19" s="14"/>
+      <c r="CK19" s="12"/>
+      <c r="CL19" s="13"/>
+      <c r="CM19" s="12"/>
+      <c r="CN19" s="14"/>
+      <c r="CO19" s="12"/>
+      <c r="CP19" s="14"/>
+      <c r="CQ19" s="15"/>
+      <c r="CR19" s="16"/>
+      <c r="CS19" s="16"/>
+      <c r="CT19" s="17"/>
+      <c r="CU19" s="12"/>
+      <c r="CV19" s="12"/>
+    </row>
+    <row r="20" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="24"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="12"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="12"/>
+      <c r="AF20" s="14"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="14"/>
+      <c r="AI20" s="15"/>
+      <c r="AJ20" s="16"/>
+      <c r="AK20" s="16"/>
+      <c r="AL20" s="17"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="10"/>
+      <c r="AP20" s="24"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="13"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="14"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="14"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="13"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="14"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="14"/>
+      <c r="BC20" s="15"/>
+      <c r="BD20" s="16"/>
+      <c r="BE20" s="16"/>
+      <c r="BF20" s="17"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+      <c r="BI20" s="10"/>
+      <c r="BJ20" s="24"/>
+      <c r="BK20" s="12"/>
+      <c r="BL20" s="13"/>
+      <c r="BM20" s="12"/>
+      <c r="BN20" s="14"/>
+      <c r="BO20" s="12"/>
+      <c r="BP20" s="14"/>
+      <c r="BQ20" s="12"/>
+      <c r="BR20" s="13"/>
+      <c r="BS20" s="12"/>
+      <c r="BT20" s="14"/>
+      <c r="BU20" s="12"/>
+      <c r="BV20" s="14"/>
+      <c r="BW20" s="15"/>
+      <c r="BX20" s="16"/>
+      <c r="BY20" s="16"/>
+      <c r="BZ20" s="17"/>
+      <c r="CA20" s="12"/>
+      <c r="CB20" s="12"/>
+      <c r="CC20" s="10"/>
+      <c r="CD20" s="24"/>
+      <c r="CE20" s="12"/>
+      <c r="CF20" s="13"/>
+      <c r="CG20" s="12"/>
+      <c r="CH20" s="14"/>
+      <c r="CI20" s="12"/>
+      <c r="CJ20" s="14"/>
+      <c r="CK20" s="12"/>
+      <c r="CL20" s="13"/>
+      <c r="CM20" s="12"/>
+      <c r="CN20" s="14"/>
+      <c r="CO20" s="12"/>
+      <c r="CP20" s="14"/>
+      <c r="CQ20" s="15"/>
+      <c r="CR20" s="16"/>
+      <c r="CS20" s="16"/>
+      <c r="CT20" s="17"/>
+      <c r="CU20" s="12"/>
+      <c r="CV20" s="12"/>
+    </row>
+    <row r="21" spans="1:100" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="24"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="12"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="12"/>
+      <c r="AD21" s="13"/>
+      <c r="AE21" s="12"/>
+      <c r="AF21" s="14"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="14"/>
+      <c r="AI21" s="15"/>
+      <c r="AJ21" s="16"/>
+      <c r="AK21" s="16"/>
+      <c r="AL21" s="17"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="10"/>
+      <c r="AP21" s="24"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="13"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="14"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="14"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="13"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="14"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="14"/>
+      <c r="BC21" s="15"/>
+      <c r="BD21" s="16"/>
+      <c r="BE21" s="16"/>
+      <c r="BF21" s="17"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+      <c r="BI21" s="10"/>
+      <c r="BJ21" s="24"/>
+      <c r="BK21" s="12"/>
+      <c r="BL21" s="13"/>
+      <c r="BM21" s="12"/>
+      <c r="BN21" s="14"/>
+      <c r="BO21" s="12"/>
+      <c r="BP21" s="14"/>
+      <c r="BQ21" s="12"/>
+      <c r="BR21" s="13"/>
+      <c r="BS21" s="12"/>
+      <c r="BT21" s="14"/>
+      <c r="BU21" s="12"/>
+      <c r="BV21" s="14"/>
+      <c r="BW21" s="15"/>
+      <c r="BX21" s="16"/>
+      <c r="BY21" s="16"/>
+      <c r="BZ21" s="17"/>
+      <c r="CA21" s="12"/>
+      <c r="CB21" s="12"/>
+      <c r="CC21" s="10"/>
+      <c r="CD21" s="24"/>
+      <c r="CE21" s="12"/>
+      <c r="CF21" s="13"/>
+      <c r="CG21" s="12"/>
+      <c r="CH21" s="14"/>
+      <c r="CI21" s="12"/>
+      <c r="CJ21" s="14"/>
+      <c r="CK21" s="12"/>
+      <c r="CL21" s="13"/>
+      <c r="CM21" s="12"/>
+      <c r="CN21" s="14"/>
+      <c r="CO21" s="12"/>
+      <c r="CP21" s="14"/>
+      <c r="CQ21" s="15"/>
+      <c r="CR21" s="16"/>
+      <c r="CS21" s="16"/>
+      <c r="CT21" s="17"/>
+      <c r="CU21" s="12"/>
+      <c r="CV21" s="12"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:T21">
+    <sortCondition ref="A3:A21"/>
+  </sortState>
+  <mergeCells count="15">
+    <mergeCell ref="CC1:CV1"/>
+    <mergeCell ref="CG2:CJ2"/>
+    <mergeCell ref="CQ2:CT2"/>
+    <mergeCell ref="AO1:BH1"/>
+    <mergeCell ref="AS2:AV2"/>
+    <mergeCell ref="BC2:BF2"/>
+    <mergeCell ref="BI1:CB1"/>
+    <mergeCell ref="BM2:BP2"/>
+    <mergeCell ref="BW2:BZ2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="U1:AN1"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="AI2:AL2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8915E29-5EA8-4783-91B8-78ED20D63D4B}">
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="56.1" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23" style="9" customWidth="1"/>
+    <col min="2" max="16384" width="11.7109375" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="56.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" s="20" customFormat="1" ht="56.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+    </row>
+    <row r="3" spans="1:20" s="20" customFormat="1" ht="56.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="19"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+    </row>
+    <row r="4" spans="1:20" s="20" customFormat="1" ht="56.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="19"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="12"/>
+    </row>
+    <row r="5" spans="1:20" s="20" customFormat="1" ht="56.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="22"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+    </row>
+    <row r="6" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="12"/>
+      <c r="T6" s="12"/>
+    </row>
+    <row r="7" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+    </row>
+    <row r="8" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+    </row>
+    <row r="9" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+    </row>
+    <row r="10" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+    </row>
+    <row r="11" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+    </row>
+    <row r="12" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="12"/>
+      <c r="T12" s="12"/>
+    </row>
+    <row r="13" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+    </row>
+    <row r="14" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+    </row>
+    <row r="15" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+    </row>
+    <row r="16" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+    </row>
+    <row r="17" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+    </row>
+    <row r="18" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+    </row>
+    <row r="19" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+    </row>
+    <row r="20" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T5">
+    <sortCondition ref="A2:A5"/>
+  </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="O1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A16E60-14B5-4052-ACC4-0F31E0E16243}">
   <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.28515625" style="19" customWidth="1"/>
-    <col min="2" max="16384" width="11.7109375" style="19"/>
+    <col min="1" max="1" width="23.28515625" style="18" customWidth="1"/>
+    <col min="2" max="16384" width="11.7109375" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="57" customHeight="1" x14ac:dyDescent="0.25">
@@ -1388,16 +6952,16 @@
         <v>9</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="8"/>
       <c r="S1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="57" customHeight="1" x14ac:dyDescent="0.25">
@@ -1826,508 +7390,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8915E29-5EA8-4783-91B8-78ED20D63D4B}">
-  <dimension ref="A1:T20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.7109375" defaultRowHeight="56.1" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23" style="9" customWidth="1"/>
-    <col min="2" max="16384" width="11.7109375" style="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:20" ht="56.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="56.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-    </row>
-    <row r="3" spans="1:20" ht="56.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="16"/>
-      <c r="Q3" s="16"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-    </row>
-    <row r="4" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-    </row>
-    <row r="5" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-    </row>
-    <row r="6" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="17"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-    </row>
-    <row r="7" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="17"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-    </row>
-    <row r="8" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-    </row>
-    <row r="9" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-    </row>
-    <row r="10" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-    </row>
-    <row r="11" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-    </row>
-    <row r="12" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-    </row>
-    <row r="13" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-    </row>
-    <row r="14" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-    </row>
-    <row r="15" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="17"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-    </row>
-    <row r="16" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="17"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-    </row>
-    <row r="17" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="17"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-    </row>
-    <row r="18" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-    </row>
-    <row r="19" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="17"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-    </row>
-    <row r="20" spans="1:20" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="17"/>
-      <c r="S20" s="12"/>
-      <c r="T20" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="O1:R1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>